--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U22"/>
+  <dimension ref="A2:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,10 @@
     <col width="9" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="46" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="46" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -539,8 +542,11 @@
       <c r="O3" s="3" t="n">
         <v>46276</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="3" t="n">
         <v>46283</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -631,22 +637,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -713,20 +734,31 @@
         <f>P5/$D$5</f>
         <v/>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="10">
         <f>S5-P5</f>
         <v/>
       </c>
-      <c r="S5" s="12" t="n">
+      <c r="S5" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="11">
         <f>S5/$D$5</f>
         <v/>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 56 units, Block B: 41 units</t>
+      <c r="U5" s="12">
+        <f>V5-S5</f>
+        <v/>
+      </c>
+      <c r="V5" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="W5" s="13">
+        <f>V5/$D$5</f>
+        <v/>
+      </c>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 57 units, Block B: 41 units</t>
         </is>
       </c>
     </row>
@@ -791,20 +823,31 @@
         <f>P6/$D$6</f>
         <v/>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="10">
         <f>S6-P6</f>
         <v/>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" s="10" t="n">
         <v>347</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="11">
         <f>S6/$D$6</f>
         <v/>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 203 units, Block B: 99 units</t>
+      <c r="U6" s="12">
+        <f>V6-S6</f>
+        <v/>
+      </c>
+      <c r="V6" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="W6" s="13">
+        <f>V6/$D$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 45 units, Block A2: 204 units, Block B: 101 units</t>
         </is>
       </c>
     </row>
@@ -838,10 +881,13 @@
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
       <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="11" t="n"/>
+      <c r="U7" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -877,10 +923,13 @@
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="11" t="n"/>
-      <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="11" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="12" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -947,20 +996,31 @@
         <f>P9/$D$9</f>
         <v/>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="10">
         <f>S9-P9</f>
         <v/>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" s="10" t="n">
         <v>343</v>
       </c>
-      <c r="T9" s="13">
+      <c r="T9" s="11">
         <f>S9/$D$9</f>
         <v/>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block L: 343 units</t>
+      <c r="U9" s="12">
+        <f>V9-S9</f>
+        <v/>
+      </c>
+      <c r="V9" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="W9" s="13">
+        <f>V9/$D$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block L: 342 units</t>
         </is>
       </c>
     </row>
@@ -1025,18 +1085,29 @@
         <f>P10/$D$10</f>
         <v/>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="10">
         <f>S10-P10</f>
         <v/>
       </c>
-      <c r="S10" s="12" t="n">
+      <c r="S10" s="10" t="n">
         <v>228</v>
       </c>
-      <c r="T10" s="13">
+      <c r="T10" s="11">
         <f>S10/$D$10</f>
         <v/>
       </c>
-      <c r="U10" s="8" t="inlineStr"/>
+      <c r="U10" s="12">
+        <f>V10-S10</f>
+        <v/>
+      </c>
+      <c r="V10" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="W10" s="13">
+        <f>V10/$D$10</f>
+        <v/>
+      </c>
+      <c r="X10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1099,18 +1170,29 @@
         <f>P11/$D$11</f>
         <v/>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="10">
         <f>S11-P11</f>
         <v/>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="10" t="n">
         <v>273</v>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="11">
         <f>S11/$D$11</f>
         <v/>
       </c>
-      <c r="U11" s="8" t="inlineStr"/>
+      <c r="U11" s="12">
+        <f>V11-S11</f>
+        <v/>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="W11" s="13">
+        <f>V11/$D$11</f>
+        <v/>
+      </c>
+      <c r="X11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1173,18 +1255,29 @@
         <f>P12/$D$12</f>
         <v/>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="10">
         <f>S12-P12</f>
         <v/>
       </c>
-      <c r="S12" s="12" t="n">
+      <c r="S12" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="11">
         <f>S12/$D$12</f>
         <v/>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="U12" s="12">
+        <f>V12-S12</f>
+        <v/>
+      </c>
+      <c r="V12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="W12" s="13">
+        <f>V12/$D$12</f>
+        <v/>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>Phase 1, completed Dec 2016</t>
         </is>
@@ -1235,18 +1328,29 @@
         <f>P13/$D$13</f>
         <v/>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="10">
         <f>S13-P13</f>
         <v/>
       </c>
-      <c r="S13" s="12" t="n">
+      <c r="S13" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="T13" s="13">
+      <c r="T13" s="11">
         <f>S13/$D$13</f>
         <v/>
       </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="12">
+        <f>V13-S13</f>
+        <v/>
+      </c>
+      <c r="V13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="13">
+        <f>V13/$D$13</f>
+        <v/>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>First 16 units on TEDUH (registered as Embun); remaining 36 units not yet launched</t>
         </is>
@@ -1313,18 +1417,29 @@
         <f>P14/$D$14</f>
         <v/>
       </c>
-      <c r="R14" s="12">
+      <c r="R14" s="10">
         <f>S14-P14</f>
         <v/>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="11">
         <f>S14/$D$14</f>
         <v/>
       </c>
-      <c r="U14" s="8" t="inlineStr"/>
+      <c r="U14" s="12">
+        <f>V14-S14</f>
+        <v/>
+      </c>
+      <c r="V14" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="W14" s="13">
+        <f>V14/$D$14</f>
+        <v/>
+      </c>
+      <c r="X14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1387,18 +1502,29 @@
         <f>P15/$D$15</f>
         <v/>
       </c>
-      <c r="R15" s="12">
+      <c r="R15" s="10">
         <f>S15-P15</f>
         <v/>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="10" t="n">
         <v>222</v>
       </c>
-      <c r="T15" s="13">
+      <c r="T15" s="11">
         <f>S15/$D$15</f>
         <v/>
       </c>
-      <c r="U15" s="8" t="inlineStr"/>
+      <c r="U15" s="12">
+        <f>V15-S15</f>
+        <v/>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="W15" s="13">
+        <f>V15/$D$15</f>
+        <v/>
+      </c>
+      <c r="X15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1461,18 +1587,29 @@
         <f>P16/$D$16</f>
         <v/>
       </c>
-      <c r="R16" s="12">
+      <c r="R16" s="10">
         <f>S16-P16</f>
         <v/>
       </c>
-      <c r="S16" s="12" t="n">
+      <c r="S16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="13">
+      <c r="T16" s="11">
         <f>S16/$D$16</f>
         <v/>
       </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="U16" s="12">
+        <f>V16-S16</f>
+        <v/>
+      </c>
+      <c r="V16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="13">
+        <f>V16/$D$16</f>
+        <v/>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
         <is>
           <t>No unit found on TEDUH</t>
         </is>
@@ -1539,18 +1676,29 @@
         <f>P17/$D$17</f>
         <v/>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="10">
         <f>S17-P17</f>
         <v/>
       </c>
-      <c r="S17" s="12" t="n">
+      <c r="S17" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="T17" s="13">
+      <c r="T17" s="11">
         <f>S17/$D$17</f>
         <v/>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="U17" s="12">
+        <f>V17-S17</f>
+        <v/>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="W17" s="13">
+        <f>V17/$D$17</f>
+        <v/>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block B: 197 units</t>
         </is>
@@ -1617,18 +1765,29 @@
         <f>P18/$D$18</f>
         <v/>
       </c>
-      <c r="R18" s="12">
+      <c r="R18" s="10">
         <f>S18-P18</f>
         <v/>
       </c>
-      <c r="S18" s="12" t="n">
+      <c r="S18" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="11">
         <f>S18/$D$18</f>
         <v/>
       </c>
-      <c r="U18" s="8" t="inlineStr"/>
+      <c r="U18" s="12">
+        <f>V18-S18</f>
+        <v/>
+      </c>
+      <c r="V18" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="W18" s="13">
+        <f>V18/$D$18</f>
+        <v/>
+      </c>
+      <c r="X18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1691,18 +1850,29 @@
         <f>P19/$D$19</f>
         <v/>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="10">
         <f>S19-P19</f>
         <v/>
       </c>
-      <c r="S19" s="12" t="n">
+      <c r="S19" s="10" t="n">
         <v>456</v>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="11">
         <f>S19/$D$19</f>
         <v/>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="U19" s="12">
+        <f>V19-S19</f>
+        <v/>
+      </c>
+      <c r="V19" s="12" t="n">
+        <v>456</v>
+      </c>
+      <c r="W19" s="13">
+        <f>V19/$D$19</f>
+        <v/>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A1: 223 units, Block A2: 233 units</t>
         </is>
@@ -1769,18 +1939,29 @@
         <f>P20/$D$20</f>
         <v/>
       </c>
-      <c r="R20" s="12">
+      <c r="R20" s="10">
         <f>S20-P20</f>
         <v/>
       </c>
-      <c r="S20" s="12" t="n">
+      <c r="S20" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="T20" s="13">
+      <c r="T20" s="11">
         <f>S20/$D$20</f>
         <v/>
       </c>
-      <c r="U20" s="8" t="inlineStr"/>
+      <c r="U20" s="12">
+        <f>V20-S20</f>
+        <v/>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="W20" s="13">
+        <f>V20/$D$20</f>
+        <v/>
+      </c>
+      <c r="X20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1843,18 +2024,29 @@
         <f>P21/$D$21</f>
         <v/>
       </c>
-      <c r="R21" s="12">
+      <c r="R21" s="10">
         <f>S21-P21</f>
         <v/>
       </c>
-      <c r="S21" s="12" t="n">
+      <c r="S21" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="T21" s="13">
+      <c r="T21" s="11">
         <f>S21/$D$21</f>
         <v/>
       </c>
-      <c r="U21" s="8" t="inlineStr"/>
+      <c r="U21" s="12">
+        <f>V21-S21</f>
+        <v/>
+      </c>
+      <c r="V21" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="W21" s="13">
+        <f>V21/$D$21</f>
+        <v/>
+      </c>
+      <c r="X21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1882,18 +2074,22 @@
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="10" t="n"/>
       <c r="Q22" s="11" t="n"/>
-      <c r="R22" s="12" t="n"/>
-      <c r="S22" s="12" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="11" t="n"/>
+      <c r="U22" s="12" t="n"/>
+      <c r="V22" s="12" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:W3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="L3:N3"/>

--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X22"/>
+  <dimension ref="A2:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,10 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="46" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -545,8 +548,11 @@
       <c r="R3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -652,22 +658,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="X4" s="5" t="inlineStr">
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -745,18 +766,29 @@
         <f>S5/$D$5</f>
         <v/>
       </c>
-      <c r="U5" s="12">
+      <c r="U5" s="10">
         <f>V5-S5</f>
         <v/>
       </c>
-      <c r="V5" s="12" t="n">
+      <c r="V5" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="11">
         <f>V5/$D$5</f>
         <v/>
       </c>
-      <c r="X5" s="8" t="inlineStr">
+      <c r="X5" s="12">
+        <f>Y5-V5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="13">
+        <f>Y5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A: 57 units, Block B: 41 units</t>
         </is>
@@ -834,20 +866,31 @@
         <f>S6/$D$6</f>
         <v/>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="10">
         <f>V6-S6</f>
         <v/>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="11">
         <f>V6/$D$6</f>
         <v/>
       </c>
-      <c r="X6" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 204 units, Block B: 101 units</t>
+      <c r="X6" s="12">
+        <f>Y6-V6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <v>352</v>
+      </c>
+      <c r="Z6" s="13">
+        <f>Y6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 47 units, Block A2: 204 units, Block B: 101 units</t>
         </is>
       </c>
     </row>
@@ -884,10 +927,13 @@
       <c r="R7" s="10" t="n"/>
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="11" t="n"/>
-      <c r="U7" s="12" t="n"/>
-      <c r="V7" s="12" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="11" t="n"/>
+      <c r="X7" s="12" t="n"/>
+      <c r="Y7" s="12" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -926,10 +972,13 @@
       <c r="R8" s="10" t="n"/>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="11" t="n"/>
-      <c r="U8" s="12" t="n"/>
-      <c r="V8" s="12" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="11" t="n"/>
+      <c r="X8" s="12" t="n"/>
+      <c r="Y8" s="12" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -1007,18 +1056,29 @@
         <f>S9/$D$9</f>
         <v/>
       </c>
-      <c r="U9" s="12">
+      <c r="U9" s="10">
         <f>V9-S9</f>
         <v/>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="V9" s="10" t="n">
         <v>342</v>
       </c>
-      <c r="W9" s="13">
+      <c r="W9" s="11">
         <f>V9/$D$9</f>
         <v/>
       </c>
-      <c r="X9" s="8" t="inlineStr">
+      <c r="X9" s="12">
+        <f>Y9-V9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="Z9" s="13">
+        <f>Y9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block L: 342 units</t>
         </is>
@@ -1096,18 +1156,29 @@
         <f>S10/$D$10</f>
         <v/>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="10">
         <f>V10-S10</f>
         <v/>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" s="10" t="n">
         <v>228</v>
       </c>
-      <c r="W10" s="13">
+      <c r="W10" s="11">
         <f>V10/$D$10</f>
         <v/>
       </c>
-      <c r="X10" s="8" t="inlineStr"/>
+      <c r="X10" s="12">
+        <f>Y10-V10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="Z10" s="13">
+        <f>Y10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1181,18 +1252,29 @@
         <f>S11/$D$11</f>
         <v/>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="10">
         <f>V11-S11</f>
         <v/>
       </c>
-      <c r="V11" s="12" t="n">
+      <c r="V11" s="10" t="n">
         <v>273</v>
       </c>
-      <c r="W11" s="13">
+      <c r="W11" s="11">
         <f>V11/$D$11</f>
         <v/>
       </c>
-      <c r="X11" s="8" t="inlineStr"/>
+      <c r="X11" s="12">
+        <f>Y11-V11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="Z11" s="13">
+        <f>Y11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1266,18 +1348,29 @@
         <f>S12/$D$12</f>
         <v/>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="10">
         <f>V12-S12</f>
         <v/>
       </c>
-      <c r="V12" s="12" t="n">
+      <c r="V12" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="W12" s="13">
+      <c r="W12" s="11">
         <f>V12/$D$12</f>
         <v/>
       </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="X12" s="12">
+        <f>Y12-V12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" s="13">
+        <f>Y12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="8" t="inlineStr">
         <is>
           <t>Phase 1, completed Dec 2016</t>
         </is>
@@ -1339,18 +1432,29 @@
         <f>S13/$D$13</f>
         <v/>
       </c>
-      <c r="U13" s="12">
+      <c r="U13" s="10">
         <f>V13-S13</f>
         <v/>
       </c>
-      <c r="V13" s="12" t="n">
+      <c r="V13" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="W13" s="13">
+      <c r="W13" s="11">
         <f>V13/$D$13</f>
         <v/>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="12">
+        <f>Y13-V13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="13">
+        <f>Y13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>First 16 units on TEDUH (registered as Embun); remaining 36 units not yet launched</t>
         </is>
@@ -1428,18 +1532,29 @@
         <f>S14/$D$14</f>
         <v/>
       </c>
-      <c r="U14" s="12">
+      <c r="U14" s="10">
         <f>V14-S14</f>
         <v/>
       </c>
-      <c r="V14" s="12" t="n">
+      <c r="V14" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="W14" s="13">
+      <c r="W14" s="11">
         <f>V14/$D$14</f>
         <v/>
       </c>
-      <c r="X14" s="8" t="inlineStr"/>
+      <c r="X14" s="12">
+        <f>Y14-V14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z14" s="13">
+        <f>Y14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1513,18 +1628,29 @@
         <f>S15/$D$15</f>
         <v/>
       </c>
-      <c r="U15" s="12">
+      <c r="U15" s="10">
         <f>V15-S15</f>
         <v/>
       </c>
-      <c r="V15" s="12" t="n">
+      <c r="V15" s="10" t="n">
         <v>222</v>
       </c>
-      <c r="W15" s="13">
+      <c r="W15" s="11">
         <f>V15/$D$15</f>
         <v/>
       </c>
-      <c r="X15" s="8" t="inlineStr"/>
+      <c r="X15" s="12">
+        <f>Y15-V15</f>
+        <v/>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="Z15" s="13">
+        <f>Y15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1598,18 +1724,29 @@
         <f>S16/$D$16</f>
         <v/>
       </c>
-      <c r="U16" s="12">
+      <c r="U16" s="10">
         <f>V16-S16</f>
         <v/>
       </c>
-      <c r="V16" s="12" t="n">
+      <c r="V16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="13">
+      <c r="W16" s="11">
         <f>V16/$D$16</f>
         <v/>
       </c>
-      <c r="X16" s="8" t="inlineStr">
+      <c r="X16" s="12">
+        <f>Y16-V16</f>
+        <v/>
+      </c>
+      <c r="Y16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="13">
+        <f>Y16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="8" t="inlineStr">
         <is>
           <t>No unit found on TEDUH</t>
         </is>
@@ -1687,18 +1824,29 @@
         <f>S17/$D$17</f>
         <v/>
       </c>
-      <c r="U17" s="12">
+      <c r="U17" s="10">
         <f>V17-S17</f>
         <v/>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="W17" s="13">
+      <c r="W17" s="11">
         <f>V17/$D$17</f>
         <v/>
       </c>
-      <c r="X17" s="8" t="inlineStr">
+      <c r="X17" s="12">
+        <f>Y17-V17</f>
+        <v/>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="Z17" s="13">
+        <f>Y17/$D$17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block B: 197 units</t>
         </is>
@@ -1776,18 +1924,29 @@
         <f>S18/$D$18</f>
         <v/>
       </c>
-      <c r="U18" s="12">
+      <c r="U18" s="10">
         <f>V18-S18</f>
         <v/>
       </c>
-      <c r="V18" s="12" t="n">
+      <c r="V18" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="W18" s="13">
+      <c r="W18" s="11">
         <f>V18/$D$18</f>
         <v/>
       </c>
-      <c r="X18" s="8" t="inlineStr"/>
+      <c r="X18" s="12">
+        <f>Y18-V18</f>
+        <v/>
+      </c>
+      <c r="Y18" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z18" s="13">
+        <f>Y18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1861,18 +2020,29 @@
         <f>S19/$D$19</f>
         <v/>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="10">
         <f>V19-S19</f>
         <v/>
       </c>
-      <c r="V19" s="12" t="n">
+      <c r="V19" s="10" t="n">
         <v>456</v>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="11">
         <f>V19/$D$19</f>
         <v/>
       </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="X19" s="12">
+        <f>Y19-V19</f>
+        <v/>
+      </c>
+      <c r="Y19" s="12" t="n">
+        <v>456</v>
+      </c>
+      <c r="Z19" s="13">
+        <f>Y19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A1: 223 units, Block A2: 233 units</t>
         </is>
@@ -1950,18 +2120,29 @@
         <f>S20/$D$20</f>
         <v/>
       </c>
-      <c r="U20" s="12">
+      <c r="U20" s="10">
         <f>V20-S20</f>
         <v/>
       </c>
-      <c r="V20" s="12" t="n">
+      <c r="V20" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="W20" s="13">
+      <c r="W20" s="11">
         <f>V20/$D$20</f>
         <v/>
       </c>
-      <c r="X20" s="8" t="inlineStr"/>
+      <c r="X20" s="12">
+        <f>Y20-V20</f>
+        <v/>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="Z20" s="13">
+        <f>Y20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2035,18 +2216,29 @@
         <f>S21/$D$21</f>
         <v/>
       </c>
-      <c r="U21" s="12">
+      <c r="U21" s="10">
         <f>V21-S21</f>
         <v/>
       </c>
-      <c r="V21" s="12" t="n">
+      <c r="V21" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="W21" s="13">
+      <c r="W21" s="11">
         <f>V21/$D$21</f>
         <v/>
       </c>
-      <c r="X21" s="8" t="inlineStr"/>
+      <c r="X21" s="12">
+        <f>Y21-V21</f>
+        <v/>
+      </c>
+      <c r="Y21" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="13">
+        <f>Y21/$D$21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2077,19 +2269,23 @@
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="11" t="n"/>
-      <c r="U22" s="12" t="n"/>
-      <c r="V22" s="12" t="n"/>
-      <c r="W22" s="13" t="n"/>
-      <c r="X22" s="8" t="inlineStr">
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="11" t="n"/>
+      <c r="X22" s="12" t="n"/>
+      <c r="Y22" s="12" t="n"/>
+      <c r="Z22" s="13" t="n"/>
+      <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="X3:Z3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="L3:N3"/>

--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AA22"/>
+  <dimension ref="A2:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,10 @@
     <col width="9" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
-    <col width="46" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="46" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -551,8 +554,11 @@
       <c r="U3" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="X3" s="3" t="n">
         <v>46297</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -673,22 +679,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="Y4" s="6" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr">
+      <c r="AA4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AB4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AC4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -777,18 +798,29 @@
         <f>V5/$D$5</f>
         <v/>
       </c>
-      <c r="X5" s="12">
+      <c r="X5" s="10">
         <f>Y5-V5</f>
         <v/>
       </c>
-      <c r="Y5" s="12" t="n">
+      <c r="Y5" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="Z5" s="11">
         <f>Y5/$D$5</f>
         <v/>
       </c>
-      <c r="AA5" s="8" t="inlineStr">
+      <c r="AA5" s="12">
+        <f>AB5-Y5</f>
+        <v/>
+      </c>
+      <c r="AB5" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="AC5" s="13">
+        <f>AB5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A: 57 units, Block B: 41 units</t>
         </is>
@@ -877,20 +909,31 @@
         <f>V6/$D$6</f>
         <v/>
       </c>
-      <c r="X6" s="12">
+      <c r="X6" s="10">
         <f>Y6-V6</f>
         <v/>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" s="10" t="n">
         <v>352</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="11">
         <f>Y6/$D$6</f>
         <v/>
       </c>
-      <c r="AA6" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A1: 47 units, Block A2: 204 units, Block B: 101 units</t>
+      <c r="AA6" s="12">
+        <f>AB6-Y6</f>
+        <v/>
+      </c>
+      <c r="AB6" s="12" t="n">
+        <v>353</v>
+      </c>
+      <c r="AC6" s="13">
+        <f>AB6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 48 units, Block A2: 204 units, Block B: 101 units</t>
         </is>
       </c>
     </row>
@@ -930,10 +973,13 @@
       <c r="U7" s="10" t="n"/>
       <c r="V7" s="10" t="n"/>
       <c r="W7" s="11" t="n"/>
-      <c r="X7" s="12" t="n"/>
-      <c r="Y7" s="12" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-      <c r="AA7" s="8" t="inlineStr">
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="11" t="n"/>
+      <c r="AA7" s="12" t="n"/>
+      <c r="AB7" s="12" t="n"/>
+      <c r="AC7" s="13" t="n"/>
+      <c r="AD7" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -975,10 +1021,13 @@
       <c r="U8" s="10" t="n"/>
       <c r="V8" s="10" t="n"/>
       <c r="W8" s="11" t="n"/>
-      <c r="X8" s="12" t="n"/>
-      <c r="Y8" s="12" t="n"/>
-      <c r="Z8" s="13" t="n"/>
-      <c r="AA8" s="8" t="inlineStr">
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="11" t="n"/>
+      <c r="AA8" s="12" t="n"/>
+      <c r="AB8" s="12" t="n"/>
+      <c r="AC8" s="13" t="n"/>
+      <c r="AD8" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -1067,18 +1116,29 @@
         <f>V9/$D$9</f>
         <v/>
       </c>
-      <c r="X9" s="12">
+      <c r="X9" s="10">
         <f>Y9-V9</f>
         <v/>
       </c>
-      <c r="Y9" s="12" t="n">
+      <c r="Y9" s="10" t="n">
         <v>342</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="Z9" s="11">
         <f>Y9/$D$9</f>
         <v/>
       </c>
-      <c r="AA9" s="8" t="inlineStr">
+      <c r="AA9" s="12">
+        <f>AB9-Y9</f>
+        <v/>
+      </c>
+      <c r="AB9" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="AC9" s="13">
+        <f>AB9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block L: 342 units</t>
         </is>
@@ -1167,18 +1227,29 @@
         <f>V10/$D$10</f>
         <v/>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="10">
         <f>Y10-V10</f>
         <v/>
       </c>
-      <c r="Y10" s="12" t="n">
+      <c r="Y10" s="10" t="n">
         <v>228</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="Z10" s="11">
         <f>Y10/$D$10</f>
         <v/>
       </c>
-      <c r="AA10" s="8" t="inlineStr"/>
+      <c r="AA10" s="12">
+        <f>AB10-Y10</f>
+        <v/>
+      </c>
+      <c r="AB10" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="AC10" s="13">
+        <f>AB10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AD10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1263,18 +1334,29 @@
         <f>V11/$D$11</f>
         <v/>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="10">
         <f>Y11-V11</f>
         <v/>
       </c>
-      <c r="Y11" s="12" t="n">
+      <c r="Y11" s="10" t="n">
         <v>273</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="Z11" s="11">
         <f>Y11/$D$11</f>
         <v/>
       </c>
-      <c r="AA11" s="8" t="inlineStr"/>
+      <c r="AA11" s="12">
+        <f>AB11-Y11</f>
+        <v/>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="AC11" s="13">
+        <f>AB11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1359,18 +1441,29 @@
         <f>V12/$D$12</f>
         <v/>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="10">
         <f>Y12-V12</f>
         <v/>
       </c>
-      <c r="Y12" s="12" t="n">
+      <c r="Y12" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="Z12" s="11">
         <f>Y12/$D$12</f>
         <v/>
       </c>
-      <c r="AA12" s="8" t="inlineStr">
+      <c r="AA12" s="12">
+        <f>AB12-Y12</f>
+        <v/>
+      </c>
+      <c r="AB12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC12" s="13">
+        <f>AB12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="8" t="inlineStr">
         <is>
           <t>Phase 1, completed Dec 2016</t>
         </is>
@@ -1443,18 +1536,29 @@
         <f>V13/$D$13</f>
         <v/>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="10">
         <f>Y13-V13</f>
         <v/>
       </c>
-      <c r="Y13" s="12" t="n">
+      <c r="Y13" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z13" s="13">
+      <c r="Z13" s="11">
         <f>Y13/$D$13</f>
         <v/>
       </c>
-      <c r="AA13" s="8" t="inlineStr">
+      <c r="AA13" s="12">
+        <f>AB13-Y13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC13" s="13">
+        <f>AB13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="8" t="inlineStr">
         <is>
           <t>First 16 units on TEDUH (registered as Embun); remaining 36 units not yet launched</t>
         </is>
@@ -1543,18 +1647,29 @@
         <f>V14/$D$14</f>
         <v/>
       </c>
-      <c r="X14" s="12">
+      <c r="X14" s="10">
         <f>Y14-V14</f>
         <v/>
       </c>
-      <c r="Y14" s="12" t="n">
+      <c r="Y14" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="Z14" s="11">
         <f>Y14/$D$14</f>
         <v/>
       </c>
-      <c r="AA14" s="8" t="inlineStr"/>
+      <c r="AA14" s="12">
+        <f>AB14-Y14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC14" s="13">
+        <f>AB14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1639,18 +1754,29 @@
         <f>V15/$D$15</f>
         <v/>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="10">
         <f>Y15-V15</f>
         <v/>
       </c>
-      <c r="Y15" s="12" t="n">
+      <c r="Y15" s="10" t="n">
         <v>222</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="Z15" s="11">
         <f>Y15/$D$15</f>
         <v/>
       </c>
-      <c r="AA15" s="8" t="inlineStr"/>
+      <c r="AA15" s="12">
+        <f>AB15-Y15</f>
+        <v/>
+      </c>
+      <c r="AB15" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC15" s="13">
+        <f>AB15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1735,18 +1861,29 @@
         <f>V16/$D$16</f>
         <v/>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="10">
         <f>Y16-V16</f>
         <v/>
       </c>
-      <c r="Y16" s="12" t="n">
+      <c r="Y16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="Z16" s="11">
         <f>Y16/$D$16</f>
         <v/>
       </c>
-      <c r="AA16" s="8" t="inlineStr">
+      <c r="AA16" s="12">
+        <f>AB16-Y16</f>
+        <v/>
+      </c>
+      <c r="AB16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="13">
+        <f>AB16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="8" t="inlineStr">
         <is>
           <t>No unit found on TEDUH</t>
         </is>
@@ -1835,18 +1972,29 @@
         <f>V17/$D$17</f>
         <v/>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="10">
         <f>Y17-V17</f>
         <v/>
       </c>
-      <c r="Y17" s="12" t="n">
+      <c r="Y17" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="Z17" s="13">
+      <c r="Z17" s="11">
         <f>Y17/$D$17</f>
         <v/>
       </c>
-      <c r="AA17" s="8" t="inlineStr">
+      <c r="AA17" s="12">
+        <f>AB17-Y17</f>
+        <v/>
+      </c>
+      <c r="AB17" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="AC17" s="13">
+        <f>AB17/$D$17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block B: 197 units</t>
         </is>
@@ -1935,18 +2083,29 @@
         <f>V18/$D$18</f>
         <v/>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="10">
         <f>Y18-V18</f>
         <v/>
       </c>
-      <c r="Y18" s="12" t="n">
+      <c r="Y18" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="Z18" s="11">
         <f>Y18/$D$18</f>
         <v/>
       </c>
-      <c r="AA18" s="8" t="inlineStr"/>
+      <c r="AA18" s="12">
+        <f>AB18-Y18</f>
+        <v/>
+      </c>
+      <c r="AB18" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="AC18" s="13">
+        <f>AB18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2031,18 +2190,29 @@
         <f>V19/$D$19</f>
         <v/>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="10">
         <f>Y19-V19</f>
         <v/>
       </c>
-      <c r="Y19" s="12" t="n">
+      <c r="Y19" s="10" t="n">
         <v>456</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="11">
         <f>Y19/$D$19</f>
         <v/>
       </c>
-      <c r="AA19" s="8" t="inlineStr">
+      <c r="AA19" s="12">
+        <f>AB19-Y19</f>
+        <v/>
+      </c>
+      <c r="AB19" s="12" t="n">
+        <v>456</v>
+      </c>
+      <c r="AC19" s="13">
+        <f>AB19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AD19" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A1: 223 units, Block A2: 233 units</t>
         </is>
@@ -2131,18 +2301,29 @@
         <f>V20/$D$20</f>
         <v/>
       </c>
-      <c r="X20" s="12">
+      <c r="X20" s="10">
         <f>Y20-V20</f>
         <v/>
       </c>
-      <c r="Y20" s="12" t="n">
+      <c r="Y20" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="Z20" s="13">
+      <c r="Z20" s="11">
         <f>Y20/$D$20</f>
         <v/>
       </c>
-      <c r="AA20" s="8" t="inlineStr"/>
+      <c r="AA20" s="12">
+        <f>AB20-Y20</f>
+        <v/>
+      </c>
+      <c r="AB20" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="AC20" s="13">
+        <f>AB20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2227,18 +2408,29 @@
         <f>V21/$D$21</f>
         <v/>
       </c>
-      <c r="X21" s="12">
+      <c r="X21" s="10">
         <f>Y21-V21</f>
         <v/>
       </c>
-      <c r="Y21" s="12" t="n">
+      <c r="Y21" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="Z21" s="13">
+      <c r="Z21" s="11">
         <f>Y21/$D$21</f>
         <v/>
       </c>
-      <c r="AA21" s="8" t="inlineStr"/>
+      <c r="AA21" s="12">
+        <f>AB21-Y21</f>
+        <v/>
+      </c>
+      <c r="AB21" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC21" s="13">
+        <f>AB21/$D$21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2272,23 +2464,27 @@
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
       <c r="W22" s="11" t="n"/>
-      <c r="X22" s="12" t="n"/>
-      <c r="Y22" s="12" t="n"/>
-      <c r="Z22" s="13" t="n"/>
-      <c r="AA22" s="8" t="inlineStr">
+      <c r="X22" s="10" t="n"/>
+      <c r="Y22" s="10" t="n"/>
+      <c r="Z22" s="11" t="n"/>
+      <c r="AA22" s="12" t="n"/>
+      <c r="AB22" s="12" t="n"/>
+      <c r="AC22" s="13" t="n"/>
+      <c r="AD22" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="L3:N3"/>
+    <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:Q3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
